--- a/tests/archean/settings.xlsx
+++ b/tests/archean/settings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ttntr\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sophiamail-my.sharepoint.com/personal/01043753_sophiamail_sophia_ac_jp/Documents/PATMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9E09E891-4105-471F-AF1C-74BEE7575B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05286D34-FFD7-4B66-8FED-D3652D5F2A65}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{06C37378-65EC-8349-A749-809AD85E710E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{06C37378-65EC-8349-A749-809AD85E710E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -136,10 +136,11 @@
     <t>SO4:gd(j), S8:2.62d-4</t>
   </si>
   <si>
-    <t>CH4:0.1, O2:0.1, NH3:0.1, H2O2:0.1, HO2:0.1, CH2O:0.1, CHO:0.1, OH:0.1, O:0.1, H:0.1, CO:0.1, HOCO:0.1, CH3:0.1, HCN:0.1</t>
-  </si>
-  <si>
     <t>H2S : 3.85d9/1d5/11d0, SO2 : 10d0*3.85d9/1d5/11d0, CO : 3d9/1d5, H2 : 1d10/1d5, NH3 : 5.3d9/1d5</t>
+  </si>
+  <si>
+    <t>CH4:0.1, O2:0.1, NH3:0.1, H2O2:0.1, HO2:0.1, CH2O:0.1, HCO:0.1, OH:0.1, O:0.1, H:0.1, CO:0.1, HOCO:0.1, CH3:0.1, HCN:0.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -150,7 +151,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -163,7 +164,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -546,14 +547,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8537C3E-DE4A-A54B-9562-BA16146EEF99}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="70.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -564,7 +565,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -575,7 +576,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -586,7 +587,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -597,7 +598,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -608,7 +609,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -619,7 +620,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -630,7 +631,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -641,7 +642,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -652,7 +653,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -663,7 +664,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -674,7 +675,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -685,7 +686,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -696,7 +697,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -707,7 +708,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -715,10 +716,10 @@
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -726,7 +727,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
